--- a/Metadata.xlsx
+++ b/Metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mseduculiegebe-my.sharepoint.com/personal/nicolas_conserva_student_uliege_be/Documents/Documents/Université de Liège - Sciences Biologiques/Master thesis/Modelization/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/nicolas_conserva_uclouvain_be/Documents/Article (re)submission - Journal of Applied ecology/Data_and_Rscripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5EFD0C7B-2793-4D10-A88A-174AFF64A019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFA75E46-8144-4219-98B4-D55835DB5D89}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{5EFD0C7B-2793-4D10-A88A-174AFF64A019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F014D1-D5C6-4D9E-8DC0-D7C37799DAC0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-4530" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>Variable header</t>
   </si>
@@ -78,12 +78,6 @@
     <t>Edge Density (m/ha)</t>
   </si>
   <si>
-    <t>ENN_MN</t>
-  </si>
-  <si>
-    <t>Mean Nearest Neighbour distance (m)</t>
-  </si>
-  <si>
     <t>Riparian_Forest</t>
   </si>
   <si>
@@ -111,70 +105,16 @@
     <t>Percentage of Mosaic of Uses cover (%)</t>
   </si>
   <si>
-    <t>Primary_Forest</t>
-  </si>
-  <si>
-    <t>Percentage of Primary Forest (% per municipality)</t>
-  </si>
-  <si>
     <t>Secondary_Forest</t>
   </si>
   <si>
     <t>Percentage of Secondary Forest (% per municipality)</t>
   </si>
   <si>
-    <t>alt_1</t>
-  </si>
-  <si>
-    <t>Percentage of pixels within the category 1 of altitude classes (%)</t>
-  </si>
-  <si>
-    <t>alt_2</t>
-  </si>
-  <si>
-    <t>Percentage of pixels within the category 2 of altitude classes (%)</t>
-  </si>
-  <si>
-    <t>alt_3</t>
-  </si>
-  <si>
-    <t>Percentage of pixels within the category 3 of altitude classes (%)</t>
-  </si>
-  <si>
-    <t>alt_4</t>
-  </si>
-  <si>
-    <t>Percentage of pixels within the category 4 of altitude classes (%)</t>
-  </si>
-  <si>
-    <t>alt_5</t>
-  </si>
-  <si>
-    <t>Percentage of pixels within the category 5 of altitude classes (%)</t>
-  </si>
-  <si>
-    <t>steep_slope</t>
-  </si>
-  <si>
-    <t>Percentage of steep slope (%)</t>
-  </si>
-  <si>
     <t>temp</t>
   </si>
   <si>
     <t>Mean annual temperature (°C)</t>
-  </si>
-  <si>
-    <t>cold_temp</t>
-  </si>
-  <si>
-    <t>Mean temperature of the coldest month of the year (°C)</t>
-  </si>
-  <si>
-    <t>hot_temp</t>
-  </si>
-  <si>
-    <t>Mean temperature of the hottest month of the year (°C)</t>
   </si>
   <si>
     <t>prec</t>
@@ -245,31 +185,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> when no forest patch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>numerical continue,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with NA value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when no forest patch or only 1</t>
     </r>
   </si>
 </sst>
@@ -615,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.77734375" style="1" customWidth="1"/>
@@ -686,7 +601,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -697,10 +612,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -708,18 +623,18 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -730,7 +645,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -741,10 +656,10 @@
         <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -755,7 +670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -763,7 +678,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -777,7 +692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -785,128 +700,18 @@
         <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
